--- a/pensum/ok02/OK02_Viktige_begreper_Oppgaver_v6.xlsx
+++ b/pensum/ok02/OK02_Viktige_begreper_Oppgaver_v6.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="194">
   <si>
     <t xml:space="preserve">Viktige bedriftsøkonomiske begreper: oppgaver til kapittel 2</t>
   </si>
@@ -145,9 +145,18 @@
     <t xml:space="preserve">Gule celler fyller du inn. Grønne regnes ut av arket. Sjekken til høyre forteller om svaret stemmer, og hva du bør se på hvis ikke.</t>
   </si>
   <si>
+    <t xml:space="preserve">Fast</t>
+  </si>
+  <si>
     <t xml:space="preserve">Oppgave 1B: Fast eller variabel: tolv kostnader hos Nordlys</t>
   </si>
   <si>
+    <t xml:space="preserve">Variabel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kommer an på</t>
+  </si>
+  <si>
     <t xml:space="preserve">Det er juli. Halve Nordlys har ferie, og nesten ingen jobber utføres. Kari går gjennom regningene og spør for hver av dem: kommer denne uansett, eller stopper den når det ikke er jobber?</t>
   </si>
   <si>
@@ -217,7 +226,16 @@
     <t xml:space="preserve">Med egne ord: hva skjer med de faste kostnadene per time når det blir stille, og hva bør det bety for timeprisen? (To–tre setninger.)</t>
   </si>
   <si>
+    <t xml:space="preserve">Hun har glemt varekjøpet i mai</t>
+  </si>
+  <si>
     <t xml:space="preserve">Oppgave 1C: Nordlys mars til mai: hvorfor var kontoen trang?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hun har brukt feil lagertall</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ingenting, 280 000 er riktig</t>
   </si>
   <si>
     <t xml:space="preserve">Samme sak som i 1A, nå for hele våren. Lageret var 1 250 000 kr 1. mars, februarkjøpet var 760 000 kr, og Polarlys gir 30 dagers kreditt. Kari sier at regnskapet viste overskudd i april, men at kontoen var trang.</t>
@@ -309,7 +327,13 @@
     <t xml:space="preserve">g) Eieren vil sette timeprisen ut fra timelønna, 311 kr. Hva sier du til ham? Bruk tallene fra d til f og timeprisen 890 kr.</t>
   </si>
   <si>
+    <t xml:space="preserve">Direkte</t>
+  </si>
+  <si>
     <t xml:space="preserve">Oppgave 2B: Jobb 2614 hos Hansen: direkte, indirekte og selvkost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indirekte</t>
   </si>
   <si>
     <t xml:space="preserve">Nordlys bytter sikringsskap hos Hansen, jobbnummer 2614. Montørene bruker 14 timer, materiellet koster 9 800 kr, og kjøringen 800 kr. Ida skal finne ut hva jobben koster Nordlys.</t>
@@ -780,7 +804,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -859,6 +883,10 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -1552,7 +1580,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:G39"/>
+  <dimension ref="B1:Z39"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -1560,17 +1588,26 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="56"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="26" min="26" style="0" width="13"/>
   </cols>
   <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z1" s="0" t="s">
+        <v>38</v>
+      </c>
+    </row>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
+      <c r="Z2" s="20" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="6" t="s">
@@ -1581,6 +1618,9 @@
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
+      <c r="Z3" s="20" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="7" t="s">
@@ -1591,16 +1631,22 @@
       <c r="E4" s="7"/>
       <c r="F4" s="7"/>
       <c r="G4" s="7"/>
+      <c r="Z4" s="20" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="8" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
       <c r="E5" s="8"/>
       <c r="F5" s="8"/>
       <c r="G5" s="8"/>
+      <c r="Z5" s="20" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="7" t="s">
@@ -1611,263 +1657,364 @@
       <c r="E6" s="7"/>
       <c r="F6" s="7"/>
       <c r="G6" s="7"/>
+      <c r="Z6" s="20" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="8" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
       <c r="E7" s="8"/>
       <c r="F7" s="8"/>
       <c r="G7" s="8"/>
+      <c r="Z7" s="20" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z8" s="0" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="7" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
       <c r="E9" s="7"/>
       <c r="F9" s="7"/>
       <c r="G9" s="7"/>
+      <c r="Z9" s="20" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="8" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
       <c r="E10" s="8"/>
       <c r="F10" s="8"/>
       <c r="G10" s="8"/>
+      <c r="Z10" s="20" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z11" s="0" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="C12" s="20"/>
-      <c r="D12" s="20"/>
-      <c r="E12" s="20"/>
-      <c r="F12" s="20"/>
-      <c r="G12" s="20"/>
+      <c r="B12" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="C12" s="21"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="21"/>
+      <c r="F12" s="21"/>
+      <c r="G12" s="21"/>
+      <c r="Z12" s="20" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="21" t="s">
-        <v>44</v>
+      <c r="B13" s="22" t="s">
+        <v>47</v>
       </c>
       <c r="C13" s="18"/>
-      <c r="G13" s="22" t="str">
+      <c r="G13" s="23" t="str">
         <f aca="false">IF(C13="","Velg i nedtrekksmenyen.",IF(C13="Fast","Riktig. Husleia kommer uansett om det er jobber eller ikke. Boka kaller det en kapasitetskostnad.","Ikke riktig. Husleia kommer uansett om det er jobber eller ikke. Boka kaller det en kapasitetskostnad."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z13" s="20" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="21" t="s">
-        <v>45</v>
+      <c r="B14" s="22" t="s">
+        <v>48</v>
       </c>
       <c r="C14" s="18"/>
-      <c r="G14" s="22" t="str">
+      <c r="G14" s="23" t="str">
         <f aca="false">IF(C14="","Velg i nedtrekksmenyen.",IF(C14="Fast","Riktig. Forsikringen løper hele året, uavhengig av antall jobber.","Ikke riktig. Forsikringen løper hele året, uavhengig av antall jobber."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z14" s="20" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="21" t="s">
-        <v>46</v>
+      <c r="B15" s="22" t="s">
+        <v>49</v>
       </c>
       <c r="C15" s="18"/>
-      <c r="G15" s="22" t="str">
+      <c r="G15" s="23" t="str">
         <f aca="false">IF(C15="","Velg i nedtrekksmenyen.",IF(C15="Fast","Riktig. Bilene taper verdi enten de er ute eller inne.","Ikke riktig. Bilene taper verdi enten de er ute eller inne."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z15" s="20" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="21" t="s">
-        <v>47</v>
+      <c r="B16" s="22" t="s">
+        <v>50</v>
       </c>
       <c r="C16" s="18"/>
-      <c r="G16" s="22" t="str">
+      <c r="G16" s="23" t="str">
         <f aca="false">IF(C16="","Velg i nedtrekksmenyen.",IF(C16="Fast","Riktig. Administrasjonen er der uansett. Det er en fast kostnad.","Ikke riktig. Administrasjonen er der uansett. Det er en fast kostnad."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z16" s="20" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="21" t="s">
-        <v>48</v>
+      <c r="B17" s="22" t="s">
+        <v>51</v>
       </c>
       <c r="C17" s="18"/>
-      <c r="G17" s="22" t="str">
+      <c r="G17" s="23" t="str">
         <f aca="false">IF(C17="","Velg i nedtrekksmenyen.",IF(C17="Variabel","Riktig. Sier Nordlys nei til jobben, kjøpes ikke materiellet.","Ikke riktig. Sier Nordlys nei til jobben, kjøpes ikke materiellet."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z17" s="20" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="21" t="s">
-        <v>49</v>
+      <c r="B18" s="22" t="s">
+        <v>52</v>
       </c>
       <c r="C18" s="18"/>
-      <c r="G18" s="22" t="str">
+      <c r="G18" s="23" t="str">
         <f aca="false">IF(C18="","Velg i nedtrekksmenyen.",IF(C18="Variabel","Riktig. Innleien gjelder akkurat dette prosjektet.","Ikke riktig. Innleien gjelder akkurat dette prosjektet."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z18" s="20" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="21" t="s">
-        <v>50</v>
+      <c r="B19" s="22" t="s">
+        <v>53</v>
       </c>
       <c r="C19" s="18"/>
-      <c r="G19" s="22" t="str">
+      <c r="G19" s="23" t="str">
         <f aca="false">IF(C19="","Velg i nedtrekksmenyen.",IF(C19="Variabel","Riktig. Kjøringen følger jobben.","Ikke riktig. Kjøringen følger jobben."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z19" s="20" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="21" t="s">
-        <v>51</v>
+      <c r="B20" s="22" t="s">
+        <v>54</v>
       </c>
       <c r="C20" s="18"/>
-      <c r="G20" s="22" t="str">
+      <c r="G20" s="23" t="str">
         <f aca="false">IF(C20="","Velg i nedtrekksmenyen.",IF(C20="Variabel","Riktig. Boka regner montørlønn som variabel: timene følger jobbene (vei 1 i kapittel 2).","Ikke riktig. Boka regner montørlønn som variabel: timene følger jobbene (vei 1 i kapittel 2)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z20" s="20" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="21" t="s">
-        <v>52</v>
+      <c r="B21" s="22" t="s">
+        <v>55</v>
       </c>
       <c r="C21" s="18"/>
-      <c r="G21" s="22" t="str">
+      <c r="G21" s="23" t="str">
         <f aca="false">IF(C21="","Velg i nedtrekksmenyen.",IF(C21="Fast","Riktig. Strømmen på verkstedet varierer litt, men ikke med antall jobber. Boka regner den som fast.","Ikke riktig. Strømmen på verkstedet varierer litt, men ikke med antall jobber. Boka regner den som fast."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z21" s="20" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="21" t="s">
-        <v>53</v>
+      <c r="B22" s="22" t="s">
+        <v>56</v>
       </c>
       <c r="C22" s="18"/>
-      <c r="G22" s="22" t="str">
+      <c r="G22" s="23" t="str">
         <f aca="false">IF(C22="","Velg i nedtrekksmenyen.",IF(C22="Kommer an på","Riktig. Lønna er fast så lenge lærlingen er ansatt, men timene hans på jobbene er variable. Boka lar deg velge, men vær tydelig på hva du har valgt.","Ikke riktig. Lønna er fast så lenge lærlingen er ansatt, men timene hans på jobbene er variable. Boka lar deg velge, men vær tydelig på hva du har valgt."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z22" s="20" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="21" t="s">
-        <v>54</v>
+      <c r="B23" s="22" t="s">
+        <v>57</v>
       </c>
       <c r="C23" s="18"/>
-      <c r="G23" s="22" t="str">
+      <c r="G23" s="23" t="str">
         <f aca="false">IF(C23="","Velg i nedtrekksmenyen.",IF(C23="Kommer an på","Riktig. Fast så lenge avtalen løper. Kan sies opp eller justeres når avtalen går ut.","Ikke riktig. Fast så lenge avtalen løper. Kan sies opp eller justeres når avtalen går ut."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z23" s="20" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="21" t="s">
-        <v>55</v>
+      <c r="B24" s="22" t="s">
+        <v>58</v>
       </c>
       <c r="C24" s="18"/>
-      <c r="G24" s="22" t="str">
+      <c r="G24" s="23" t="str">
         <f aca="false">IF(C24="","Velg i nedtrekksmenyen.",IF(C24="Fast","Riktig. Kursene må tas enten det er travelt eller stille.","Ikke riktig. Kursene må tas enten det er travelt eller stille."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z24" s="20" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z25" s="0" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="7" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C26" s="7"/>
       <c r="D26" s="7"/>
       <c r="E26" s="7"/>
       <c r="F26" s="7"/>
       <c r="G26" s="7"/>
+      <c r="Z26" s="20" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="8" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
       <c r="E27" s="8"/>
       <c r="F27" s="8"/>
       <c r="G27" s="8"/>
+      <c r="Z27" s="20" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="21" t="s">
-        <v>58</v>
+      <c r="B28" s="22" t="s">
+        <v>61</v>
       </c>
       <c r="C28" s="14"/>
-      <c r="D28" s="23" t="s">
-        <v>59</v>
-      </c>
-      <c r="G28" s="22" t="str">
+      <c r="D28" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="G28" s="23" t="str">
         <f aca="false">IF(C28="","Skriv svaret i den gule cellen.",IF(ABS(C28-(ROUND(3840000/14400,0)))&lt;=1,"Riktig.",IF(ABS(C28-(ROUND(14400/3840000,0)))&lt;=1,"Du har delt motsatt vei. Det er kostnadene som skal deles på timene.",IF(ABS(C28-(ROUND(21056000/14400,0)))&lt;=1,"Du har brukt alle kostnadene, 21 056 000. Her er det bare de faste, 3 840 000.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
+      <c r="Z28" s="20" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="21" t="s">
-        <v>60</v>
+      <c r="B29" s="22" t="s">
+        <v>63</v>
       </c>
       <c r="C29" s="14"/>
-      <c r="D29" s="23" t="s">
-        <v>59</v>
-      </c>
-      <c r="G29" s="22" t="str">
+      <c r="D29" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="G29" s="23" t="str">
         <f aca="false">IF(C29="","Skriv svaret i den gule cellen.",IF(ABS(C29-(ROUND(3840000/10000,0)))&lt;=1,"Riktig.",IF(ABS(C29-(ROUND(3840000/14400,0)))&lt;=1,"Det er svaret for 14 400 timer. Nå er det 10 000 timer; del på det.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene.")))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
+      <c r="Z29" s="20" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z30" s="0" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="8" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C31" s="8"/>
       <c r="D31" s="8"/>
       <c r="E31" s="8"/>
       <c r="F31" s="8"/>
       <c r="G31" s="8"/>
+      <c r="Z31" s="20" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="24"/>
-      <c r="C32" s="24"/>
-      <c r="D32" s="24"/>
-      <c r="E32" s="24"/>
-      <c r="F32" s="24"/>
-      <c r="G32" s="24"/>
+      <c r="B32" s="25"/>
+      <c r="C32" s="25"/>
+      <c r="D32" s="25"/>
+      <c r="E32" s="25"/>
+      <c r="F32" s="25"/>
+      <c r="G32" s="25"/>
+      <c r="Z32" s="20" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B33" s="24"/>
-      <c r="C33" s="24"/>
-      <c r="D33" s="24"/>
-      <c r="E33" s="24"/>
-      <c r="F33" s="24"/>
-      <c r="G33" s="24"/>
+      <c r="B33" s="25"/>
+      <c r="C33" s="25"/>
+      <c r="D33" s="25"/>
+      <c r="E33" s="25"/>
+      <c r="F33" s="25"/>
+      <c r="G33" s="25"/>
+      <c r="Z33" s="20" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="24"/>
-      <c r="C34" s="24"/>
-      <c r="D34" s="24"/>
-      <c r="E34" s="24"/>
-      <c r="F34" s="24"/>
-      <c r="G34" s="24"/>
+      <c r="B34" s="25"/>
+      <c r="C34" s="25"/>
+      <c r="D34" s="25"/>
+      <c r="E34" s="25"/>
+      <c r="F34" s="25"/>
+      <c r="G34" s="25"/>
+      <c r="Z34" s="20" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="35" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B35" s="25" t="str">
+      <c r="B35" s="26" t="str">
         <f aca="false">IF(LEN(B32)&lt;40,"",IF(AND(ISNUMBER(SEARCH("stille",B32)),ISNUMBER(SEARCH("pris",B32))),"Bra: du har med både at de faste per time stiger når det blir stille, og hva det betyr for prisen.",IF(OR(ISNUMBER(SEARCH("stille",B32)),ISNUMBER(SEARCH("pris",B32))),"Du er på sporet. Si også hva det bør bety for timeprisen i en stille periode.","Tips: de faste kostnadene står stille i kroner, men per time stiger de når timene blir færre. Derfor må timeprisen opp, ikke ned, når det er stille.")))</f>
         <v/>
       </c>
-      <c r="C35" s="25"/>
-      <c r="D35" s="25"/>
-      <c r="E35" s="25"/>
-      <c r="F35" s="25"/>
-      <c r="G35" s="25"/>
+      <c r="C35" s="26"/>
+      <c r="D35" s="26"/>
+      <c r="E35" s="26"/>
+      <c r="F35" s="26"/>
+      <c r="G35" s="26"/>
+      <c r="Z35" s="20" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="17" t="s">
         <v>36</v>
       </c>
       <c r="C36" s="18"/>
+      <c r="Z36" s="20" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B37" s="19" t="str">
@@ -2023,51 +2170,51 @@
   </conditionalFormatting>
   <dataValidations count="13">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C13" type="list">
-      <formula1>"Fast,Variabel,Kommer an på"</formula1>
+      <formula1>$Z$1:$Z$3</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C14" type="list">
-      <formula1>"Fast,Variabel,Kommer an på"</formula1>
+      <formula1>$Z$4:$Z$6</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C15" type="list">
-      <formula1>"Fast,Variabel,Kommer an på"</formula1>
+      <formula1>$Z$7:$Z$9</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C16" type="list">
-      <formula1>"Fast,Variabel,Kommer an på"</formula1>
+      <formula1>$Z$10:$Z$12</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C17" type="list">
-      <formula1>"Fast,Variabel,Kommer an på"</formula1>
+      <formula1>$Z$13:$Z$15</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C18" type="list">
-      <formula1>"Fast,Variabel,Kommer an på"</formula1>
+      <formula1>$Z$16:$Z$18</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C19" type="list">
-      <formula1>"Fast,Variabel,Kommer an på"</formula1>
+      <formula1>$Z$19:$Z$21</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C20" type="list">
-      <formula1>"Fast,Variabel,Kommer an på"</formula1>
+      <formula1>$Z$22:$Z$24</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C21" type="list">
-      <formula1>"Fast,Variabel,Kommer an på"</formula1>
+      <formula1>$Z$25:$Z$27</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C22" type="list">
-      <formula1>"Fast,Variabel,Kommer an på"</formula1>
+      <formula1>$Z$28:$Z$30</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C23" type="list">
-      <formula1>"Fast,Variabel,Kommer an på"</formula1>
+      <formula1>$Z$31:$Z$33</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C24" type="list">
-      <formula1>"Fast,Variabel,Kommer an på"</formula1>
+      <formula1>$Z$34:$Z$36</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C36" type="list">
@@ -2090,7 +2237,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:G35"/>
+  <dimension ref="B1:Z35"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -2098,17 +2245,26 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="56"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="26" min="26" style="0" width="13"/>
   </cols>
   <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z1" s="0" t="s">
+        <v>65</v>
+      </c>
+    </row>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="5" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
+      <c r="Z2" s="20" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="6" t="s">
@@ -2119,6 +2275,9 @@
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
+      <c r="Z3" s="20" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="7" t="s">
@@ -2132,7 +2291,7 @@
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="8" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
@@ -2152,7 +2311,7 @@
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="8" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
@@ -2172,7 +2331,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="8" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
@@ -2189,7 +2348,7 @@
         <v>25</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2210,7 +2369,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="11" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C13" s="12" t="n">
         <v>890000</v>
@@ -2224,7 +2383,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="11" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C14" s="12" t="n">
         <v>1460000</v>
@@ -2238,7 +2397,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="11" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C15" s="13" t="n">
         <f aca="false">C12+C13-C14</f>
@@ -2249,7 +2408,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="11" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="C16" s="12" t="n">
         <v>760000</v>
@@ -2269,7 +2428,7 @@
     </row>
     <row r="19" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="8" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C19" s="8"/>
       <c r="D19" s="8"/>
@@ -2278,57 +2437,57 @@
       <c r="G19" s="8"/>
     </row>
     <row r="21" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="21" t="s">
-        <v>72</v>
+      <c r="B21" s="22" t="s">
+        <v>78</v>
       </c>
       <c r="C21" s="14"/>
-      <c r="D21" s="23" t="s">
-        <v>73</v>
-      </c>
-      <c r="G21" s="22" t="str">
+      <c r="D21" s="24" t="s">
+        <v>79</v>
+      </c>
+      <c r="G21" s="23" t="str">
         <f aca="false">IF(C21="","Skriv svaret i den gule cellen.",IF(C21=(E12+E13-E14),"Riktig.",IF(ABS(C21-(E12-E14))&lt;=0,"Du har glemt varekjøpet i mai, 520 000.",IF(ABS(C21-(E14-E12))&lt;=0,"Snu rekkefølgen: lager ved start minus lager ved slutt, og legg til kjøpet.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="21" t="s">
-        <v>74</v>
+      <c r="B22" s="22" t="s">
+        <v>80</v>
       </c>
       <c r="C22" s="14"/>
-      <c r="D22" s="23" t="s">
-        <v>73</v>
-      </c>
-      <c r="G22" s="22" t="str">
+      <c r="D22" s="24" t="s">
+        <v>79</v>
+      </c>
+      <c r="G22" s="23" t="str">
         <f aca="false">IF(C22="","Skriv svaret i den gule cellen.",IF(C22=(D13),"Riktig.",IF(ABS(C22-(E13))&lt;=0,"Du har tatt maikjøpet. Det betales i juni. I mai betales aprilkjøpet.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene.")))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="21" t="s">
-        <v>75</v>
+      <c r="B23" s="22" t="s">
+        <v>81</v>
       </c>
       <c r="C23" s="14"/>
-      <c r="D23" s="23" t="s">
-        <v>73</v>
-      </c>
-      <c r="G23" s="22" t="str">
+      <c r="D23" s="24" t="s">
+        <v>79</v>
+      </c>
+      <c r="G23" s="23" t="str">
         <f aca="false">IF(C23="","Skriv svaret i den gule cellen.",IF(C23=((C16+C13+D13)-(C15+(D12+D13-D14)+(E12+E13-E14))),"Riktig.",IF(ABS(C23-(C16+C13+D13))&lt;=0,"Du har svart summen av utbetalingene. Trekk fra summen av varekostnadene.",IF(ABS(C23-((C13+D13+E13)-(C15+(D12+D13-D14)+(E12+E13-E14))))&lt;=0,"Du har brukt utgiftene (kjøpene) i stedet for utbetalingene. Utbetalt i mars er februarkjøpet, 760 000.","Ikke riktig ennå. Sum utbetalt (760 000 + 890 000 + 640 000) minus sum varekostnad (680 000 + 720 000 + 800 000)."))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="21" t="s">
-        <v>76</v>
+      <c r="B25" s="22" t="s">
+        <v>82</v>
       </c>
       <c r="C25" s="18"/>
-      <c r="G25" s="22" t="str">
+      <c r="G25" s="23" t="str">
         <f aca="false">IF(C25="","Velg i nedtrekksmenyen.",IF(C25="Hun har glemt varekjøpet i mai","Riktig. Bare lagerendringen fanger ikke opp det som ble kjøpt og brukt i samme måned. Riktig: 1 380 000 + 520 000 − 1 100 000 = 800 000.","Ikke riktig. Bare lagerendringen fanger ikke opp det som ble kjøpt og brukt i samme måned. Riktig: 1 380 000 + 520 000 − 1 100 000 = 800 000."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="8" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
@@ -2337,39 +2496,39 @@
       <c r="G27" s="8"/>
     </row>
     <row r="28" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="24"/>
-      <c r="C28" s="24"/>
-      <c r="D28" s="24"/>
-      <c r="E28" s="24"/>
-      <c r="F28" s="24"/>
-      <c r="G28" s="24"/>
+      <c r="B28" s="25"/>
+      <c r="C28" s="25"/>
+      <c r="D28" s="25"/>
+      <c r="E28" s="25"/>
+      <c r="F28" s="25"/>
+      <c r="G28" s="25"/>
     </row>
     <row r="29" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="24"/>
-      <c r="C29" s="24"/>
-      <c r="D29" s="24"/>
-      <c r="E29" s="24"/>
-      <c r="F29" s="24"/>
-      <c r="G29" s="24"/>
+      <c r="B29" s="25"/>
+      <c r="C29" s="25"/>
+      <c r="D29" s="25"/>
+      <c r="E29" s="25"/>
+      <c r="F29" s="25"/>
+      <c r="G29" s="25"/>
     </row>
     <row r="30" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="24"/>
-      <c r="C30" s="24"/>
-      <c r="D30" s="24"/>
-      <c r="E30" s="24"/>
-      <c r="F30" s="24"/>
-      <c r="G30" s="24"/>
+      <c r="B30" s="25"/>
+      <c r="C30" s="25"/>
+      <c r="D30" s="25"/>
+      <c r="E30" s="25"/>
+      <c r="F30" s="25"/>
+      <c r="G30" s="25"/>
     </row>
     <row r="31" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="25" t="str">
+      <c r="B31" s="26" t="str">
         <f aca="false">IF(LEN(B28)&lt;40,"",IF(AND(ISNUMBER(SEARCH("kostnad",B28)),ISNUMBER(SEARCH("utbetal",B28)),ISNUMBER(SEARCH("lager",B28))),"Bra: du bruker kostnad, utbetaling og lager. Sjekk at du også sier hvilken måned utbetalingen gjelder (marskjøpet forfalt i april).",IF(OR(ISNUMBER(SEARCH("kostnad",B28)),ISNUMBER(SEARCH("utbetal",B28)),ISNUMBER(SEARCH("lager",B28))),"Du har med noe av det. Har du forklart forskjellen på kostnaden (det som ble brukt) og utbetalingen (det som gikk ut av kontoen), og at lageret binder penger?","Tips: resultatet regnes med kostnaden (720 000 i april). Kontoen følger utbetalingen (890 000, marskjøpet). Lageret på 1 380 000 binder penger. Bruk de tre ordene.")))</f>
         <v/>
       </c>
-      <c r="C31" s="25"/>
-      <c r="D31" s="25"/>
-      <c r="E31" s="25"/>
-      <c r="F31" s="25"/>
-      <c r="G31" s="25"/>
+      <c r="C31" s="26"/>
+      <c r="D31" s="26"/>
+      <c r="E31" s="26"/>
+      <c r="F31" s="26"/>
+      <c r="G31" s="26"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="17" t="s">
@@ -2450,7 +2609,7 @@
   </conditionalFormatting>
   <dataValidations count="2">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C25" type="list">
-      <formula1>"Hun har glemt varekjøpet i mai,Hun har brukt feil lagertall,Ingenting,280 000 er riktig"</formula1>
+      <formula1>$Z$1:$Z$3</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C32" type="list">
@@ -2485,7 +2644,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="5" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
@@ -2515,7 +2674,7 @@
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="8" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
@@ -2535,7 +2694,7 @@
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="8" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
@@ -2545,7 +2704,7 @@
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="7" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
@@ -2555,7 +2714,7 @@
     </row>
     <row r="10" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="8" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
@@ -2575,7 +2734,7 @@
     </row>
     <row r="13" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="8" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="C13" s="8"/>
       <c r="D13" s="8"/>
@@ -2584,86 +2743,86 @@
       <c r="G13" s="8"/>
     </row>
     <row r="15" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="21" t="s">
-        <v>84</v>
+      <c r="B15" s="22" t="s">
+        <v>90</v>
       </c>
       <c r="C15" s="14"/>
-      <c r="D15" s="23" t="s">
-        <v>73</v>
-      </c>
-      <c r="G15" s="22" t="str">
+      <c r="D15" s="24" t="s">
+        <v>79</v>
+      </c>
+      <c r="G15" s="23" t="str">
         <f aca="false">IF(C15="","Skriv svaret i den gule cellen.",IF(C15=(560000*1.468),"Riktig.",IF(ABS(C15-(560000*0.468))&lt;=0,"Du har regnet bare de sosiale kostnadene. Lønnskostnaden er lønna pluss de sosiale: gang med 1,468.",IF(ABS(C15-(560000))&lt;=0,"Du har svart lønna alene. De sosiale kostnadene kommer på toppen.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="21" t="s">
-        <v>85</v>
+      <c r="B16" s="22" t="s">
+        <v>91</v>
       </c>
       <c r="C16" s="14"/>
-      <c r="D16" s="23" t="s">
-        <v>73</v>
-      </c>
-      <c r="G16" s="22" t="str">
+      <c r="D16" s="24" t="s">
+        <v>79</v>
+      </c>
+      <c r="G16" s="23" t="str">
         <f aca="false">IF(C16="","Skriv svaret i den gule cellen.",IF(C16=(560000*1.494),"Riktig.",IF(ABS(C16-(560000*1.468))&lt;=0,"Det er svaret i a. Bytt 13,7 % med 16,3 %: 46,8 + 2,6 = 49,4 %.",IF(ABS(C16-(560000*1.631))&lt;=0,"Du har lagt til hele 16,3 %. Bare forskjellen fra 13,7 %, altså 2,6 prosentpoeng, kommer i tillegg.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="21" t="s">
-        <v>86</v>
+      <c r="B17" s="22" t="s">
+        <v>92</v>
       </c>
       <c r="C17" s="14"/>
-      <c r="D17" s="23" t="s">
-        <v>73</v>
-      </c>
-      <c r="G17" s="22" t="str">
+      <c r="D17" s="24" t="s">
+        <v>79</v>
+      </c>
+      <c r="G17" s="23" t="str">
         <f aca="false">IF(C17="","Skriv svaret i den gule cellen.",IF(C17=(560000*1.4),"Riktig.",IF(ABS(C17-(560000*1.468))&lt;=0,"Det er svaret i a. Pensjonen går ned fra 9,1 til 2,3 prosentpoeng: 46,8 − 6,8 = 40,0 %.",IF(ABS(C17-(560000*1.023))&lt;=0,"Du har regnet bare pensjonen. Alle de andre postene er fortsatt med: 40,0 % totalt.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="21" t="s">
-        <v>87</v>
+      <c r="B19" s="22" t="s">
+        <v>93</v>
       </c>
       <c r="C19" s="14"/>
-      <c r="D19" s="23" t="s">
-        <v>59</v>
-      </c>
-      <c r="G19" s="22" t="str">
+      <c r="D19" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="G19" s="23" t="str">
         <f aca="false">IF(C19="","Skriv svaret i den gule cellen.",IF(ABS(C19-(ROUND(560000/1800,0)))&lt;=1,"Riktig.",IF(ABS(C19-(ROUND(560000/1400,0)))&lt;=1,"Du har delt på de fakturerbare timene. Timelønna regnes på alle betalte timer, 1 800.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene.")))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="21" t="s">
-        <v>88</v>
+      <c r="B20" s="22" t="s">
+        <v>94</v>
       </c>
       <c r="C20" s="14"/>
-      <c r="D20" s="23" t="s">
-        <v>59</v>
-      </c>
-      <c r="G20" s="22" t="str">
+      <c r="D20" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="G20" s="23" t="str">
         <f aca="false">IF(C20="","Skriv svaret i den gule cellen.",IF(ABS(C20-(ROUND(560000*1.468/1800,0)))&lt;=1,"Riktig.",IF(ABS(C20-(ROUND(560000/1800,0)))&lt;=1,"Det er timelønna. Her skal lønnskostnaden med sosiale kostnader (a) deles på timene.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene.")))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="21" t="s">
-        <v>89</v>
+      <c r="B21" s="22" t="s">
+        <v>95</v>
       </c>
       <c r="C21" s="14"/>
-      <c r="D21" s="23" t="s">
-        <v>59</v>
-      </c>
-      <c r="G21" s="22" t="str">
+      <c r="D21" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="G21" s="23" t="str">
         <f aca="false">IF(C21="","Skriv svaret i den gule cellen.",IF(ABS(C21-(ROUND(560000*1.468/1400,0)))&lt;=1,"Riktig.",IF(ABS(C21-(ROUND(560000*1.468/1800,0)))&lt;=1,"Du har delt på 1 800. Kunden betaler bare for 1 400 timer, så del på 1 400.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene.")))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="8" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
@@ -2672,39 +2831,39 @@
       <c r="G23" s="8"/>
     </row>
     <row r="24" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="24"/>
-      <c r="C24" s="24"/>
-      <c r="D24" s="24"/>
-      <c r="E24" s="24"/>
-      <c r="F24" s="24"/>
-      <c r="G24" s="24"/>
+      <c r="B24" s="25"/>
+      <c r="C24" s="25"/>
+      <c r="D24" s="25"/>
+      <c r="E24" s="25"/>
+      <c r="F24" s="25"/>
+      <c r="G24" s="25"/>
     </row>
     <row r="25" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="24"/>
-      <c r="C25" s="24"/>
-      <c r="D25" s="24"/>
-      <c r="E25" s="24"/>
-      <c r="F25" s="24"/>
-      <c r="G25" s="24"/>
+      <c r="B25" s="25"/>
+      <c r="C25" s="25"/>
+      <c r="D25" s="25"/>
+      <c r="E25" s="25"/>
+      <c r="F25" s="25"/>
+      <c r="G25" s="25"/>
     </row>
     <row r="26" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="24"/>
-      <c r="C26" s="24"/>
-      <c r="D26" s="24"/>
-      <c r="E26" s="24"/>
-      <c r="F26" s="24"/>
-      <c r="G26" s="24"/>
+      <c r="B26" s="25"/>
+      <c r="C26" s="25"/>
+      <c r="D26" s="25"/>
+      <c r="E26" s="25"/>
+      <c r="F26" s="25"/>
+      <c r="G26" s="25"/>
     </row>
     <row r="27" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="25" t="str">
+      <c r="B27" s="26" t="str">
         <f aca="false">IF(LEN(B24)&lt;40,"",IF(AND(ISNUMBER(SEARCH("587",B24)),ISNUMBER(SEARCH("890",B24))),"Bra: du bruker både 587 kr per fakturerbar time og timeprisen 890. Si også hva de 303 kronene i mellom skal dekke.",IF(OR(ISNUMBER(SEARCH("587",B24)),ISNUMBER(SEARCH("890",B24))),"Du er på sporet. Ta med at hver fakturerbar time koster 587 kr i lønn, og at 890 i tillegg skal dekke bil, lokaler, utstyr og fortjeneste.","Tips: 311 er bare lønna. Med sosiale kostnader er det 457 per betalt time, og 587 per time kunden betaler for. Timeprisen 890 skal dessuten dekke bil, lokaler, utstyr og fortjeneste.")))</f>
         <v/>
       </c>
-      <c r="C27" s="25"/>
-      <c r="D27" s="25"/>
-      <c r="E27" s="25"/>
-      <c r="F27" s="25"/>
-      <c r="G27" s="25"/>
+      <c r="C27" s="26"/>
+      <c r="D27" s="26"/>
+      <c r="E27" s="26"/>
+      <c r="F27" s="26"/>
+      <c r="G27" s="26"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="17" t="s">
@@ -2820,7 +2979,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:G35"/>
+  <dimension ref="B1:Z35"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -2828,17 +2987,26 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="56"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="26" min="26" style="0" width="13"/>
   </cols>
   <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z1" s="0" t="s">
+        <v>97</v>
+      </c>
+    </row>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="5" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
+      <c r="Z2" s="20" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="6" t="s">
@@ -2849,6 +3017,9 @@
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
+      <c r="Z3" s="20" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="7" t="s">
@@ -2859,16 +3030,22 @@
       <c r="E4" s="7"/>
       <c r="F4" s="7"/>
       <c r="G4" s="7"/>
+      <c r="Z4" s="20" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="8" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
       <c r="E5" s="8"/>
       <c r="F5" s="8"/>
       <c r="G5" s="8"/>
+      <c r="Z5" s="20" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="7" t="s">
@@ -2879,130 +3056,167 @@
       <c r="E6" s="7"/>
       <c r="F6" s="7"/>
       <c r="G6" s="7"/>
+      <c r="Z6" s="20" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="8" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
       <c r="E7" s="8"/>
       <c r="F7" s="8"/>
       <c r="G7" s="8"/>
+      <c r="Z7" s="20" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z8" s="0" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="7" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
       <c r="E9" s="7"/>
       <c r="F9" s="7"/>
       <c r="G9" s="7"/>
+      <c r="Z9" s="20" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="8" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
       <c r="E10" s="8"/>
       <c r="F10" s="8"/>
       <c r="G10" s="8"/>
+      <c r="Z10" s="20" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z11" s="0" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="20" t="s">
-        <v>95</v>
-      </c>
-      <c r="C12" s="20"/>
-      <c r="D12" s="20"/>
-      <c r="E12" s="20"/>
-      <c r="F12" s="20"/>
-      <c r="G12" s="20"/>
+      <c r="B12" s="21" t="s">
+        <v>103</v>
+      </c>
+      <c r="C12" s="21"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="21"/>
+      <c r="F12" s="21"/>
+      <c r="G12" s="21"/>
+      <c r="Z12" s="20" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="21" t="s">
-        <v>96</v>
+      <c r="B13" s="22" t="s">
+        <v>104</v>
       </c>
       <c r="C13" s="18"/>
-      <c r="G13" s="22" t="str">
+      <c r="G13" s="23" t="str">
         <f aca="false">IF(C13="","Velg i nedtrekksmenyen.",IF(C13="Direkte","Riktig. Timene er brukt på akkurat denne jobben.","Ikke riktig. Timene er brukt på akkurat denne jobben."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z13" s="20" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="21" t="s">
-        <v>97</v>
+      <c r="B14" s="22" t="s">
+        <v>105</v>
       </c>
       <c r="C14" s="18"/>
-      <c r="G14" s="22" t="str">
+      <c r="G14" s="23" t="str">
         <f aca="false">IF(C14="","Velg i nedtrekksmenyen.",IF(C14="Direkte","Riktig. Materiellet er kjøpt til denne jobben.","Ikke riktig. Materiellet er kjøpt til denne jobben."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z14" s="20" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="21" t="s">
-        <v>98</v>
+      <c r="B15" s="22" t="s">
+        <v>106</v>
       </c>
       <c r="C15" s="18"/>
-      <c r="G15" s="22" t="str">
+      <c r="G15" s="23" t="str">
         <f aca="false">IF(C15="","Velg i nedtrekksmenyen.",IF(C15="Direkte","Riktig. Turen gjelder denne jobben.","Ikke riktig. Turen gjelder denne jobben."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z15" s="20" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="21" t="s">
-        <v>99</v>
+      <c r="B16" s="22" t="s">
+        <v>107</v>
       </c>
       <c r="C16" s="18"/>
-      <c r="G16" s="22" t="str">
+      <c r="G16" s="23" t="str">
         <f aca="false">IF(C16="","Velg i nedtrekksmenyen.",IF(C16="Indirekte","Riktig. Felles for alle jobbene. Fordeles med en andel.","Ikke riktig. Felles for alle jobbene. Fordeles med en andel."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z16" s="20" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="21" t="s">
-        <v>100</v>
+      <c r="B17" s="22" t="s">
+        <v>108</v>
       </c>
       <c r="C17" s="18"/>
-      <c r="G17" s="22" t="str">
+      <c r="G17" s="23" t="str">
         <f aca="false">IF(C17="","Velg i nedtrekksmenyen.",IF(C17="Indirekte","Riktig. Administrasjonen jobber for alle jobbene.","Ikke riktig. Administrasjonen jobber for alle jobbene."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="21" t="s">
-        <v>101</v>
+      <c r="B18" s="22" t="s">
+        <v>109</v>
       </c>
       <c r="C18" s="18"/>
-      <c r="G18" s="22" t="str">
+      <c r="G18" s="23" t="str">
         <f aca="false">IF(C18="","Velg i nedtrekksmenyen.",IF(C18="Indirekte","Riktig. Bilene brukes på alle jobbene.","Ikke riktig. Bilene brukes på alle jobbene."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="21" t="s">
-        <v>52</v>
+      <c r="B19" s="22" t="s">
+        <v>55</v>
       </c>
       <c r="C19" s="18"/>
-      <c r="G19" s="22" t="str">
+      <c r="G19" s="23" t="str">
         <f aca="false">IF(C19="","Velg i nedtrekksmenyen.",IF(C19="Indirekte","Riktig. Verkstedet er felles. Merk: indirekte, og samtidig variabel.","Ikke riktig. Verkstedet er felles. Merk: indirekte, og samtidig variabel."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="21" t="s">
-        <v>102</v>
+      <c r="B20" s="22" t="s">
+        <v>110</v>
       </c>
       <c r="C20" s="18"/>
-      <c r="G20" s="22" t="str">
+      <c r="G20" s="23" t="str">
         <f aca="false">IF(C20="","Velg i nedtrekksmenyen.",IF(C20="Indirekte","Riktig. Kalkulatørens tid fordeles på jobbene, selv om hun regnet på akkurat denne.","Ikke riktig. Kalkulatørens tid fordeles på jobbene, selv om hun regnet på akkurat denne."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="7" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="C22" s="7"/>
       <c r="D22" s="7"/>
@@ -3012,7 +3226,7 @@
     </row>
     <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="8" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
@@ -3021,34 +3235,34 @@
       <c r="G23" s="8"/>
     </row>
     <row r="24" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="21" t="s">
-        <v>105</v>
+      <c r="B24" s="22" t="s">
+        <v>113</v>
       </c>
       <c r="C24" s="14"/>
-      <c r="D24" s="23" t="s">
-        <v>73</v>
-      </c>
-      <c r="G24" s="22" t="str">
+      <c r="D24" s="24" t="s">
+        <v>79</v>
+      </c>
+      <c r="G24" s="23" t="str">
         <f aca="false">IF(C24="","Skriv svaret i den gule cellen.",IF(C24=(14*640+9800+800),"Riktig.",IF(ABS(C24-(14*640+9800))&lt;=0,"Du har glemt kjøringen, 800 kr.",IF(ABS(C24-(9800+800))&lt;=0,"Du har glemt montørtimene, 14 × 640 = 8 960.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="21" t="s">
-        <v>106</v>
+      <c r="B25" s="22" t="s">
+        <v>114</v>
       </c>
       <c r="C25" s="14"/>
-      <c r="D25" s="23" t="s">
-        <v>73</v>
-      </c>
-      <c r="G25" s="22" t="str">
+      <c r="D25" s="24" t="s">
+        <v>79</v>
+      </c>
+      <c r="G25" s="23" t="str">
         <f aca="false">IF(C25="","Skriv svaret i den gule cellen.",IF(C25=(14*640+9800+800+4200),"Riktig.",IF(ABS(C25-(14*640+9800+800))&lt;=0,"Det er bare de direkte. Legg til andelen indirekte, 4 200.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene.")))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="8" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
@@ -3057,39 +3271,39 @@
       <c r="G27" s="8"/>
     </row>
     <row r="28" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="24"/>
-      <c r="C28" s="24"/>
-      <c r="D28" s="24"/>
-      <c r="E28" s="24"/>
-      <c r="F28" s="24"/>
-      <c r="G28" s="24"/>
+      <c r="B28" s="25"/>
+      <c r="C28" s="25"/>
+      <c r="D28" s="25"/>
+      <c r="E28" s="25"/>
+      <c r="F28" s="25"/>
+      <c r="G28" s="25"/>
     </row>
     <row r="29" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="24"/>
-      <c r="C29" s="24"/>
-      <c r="D29" s="24"/>
-      <c r="E29" s="24"/>
-      <c r="F29" s="24"/>
-      <c r="G29" s="24"/>
+      <c r="B29" s="25"/>
+      <c r="C29" s="25"/>
+      <c r="D29" s="25"/>
+      <c r="E29" s="25"/>
+      <c r="F29" s="25"/>
+      <c r="G29" s="25"/>
     </row>
     <row r="30" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="24"/>
-      <c r="C30" s="24"/>
-      <c r="D30" s="24"/>
-      <c r="E30" s="24"/>
-      <c r="F30" s="24"/>
-      <c r="G30" s="24"/>
+      <c r="B30" s="25"/>
+      <c r="C30" s="25"/>
+      <c r="D30" s="25"/>
+      <c r="E30" s="25"/>
+      <c r="F30" s="25"/>
+      <c r="G30" s="25"/>
     </row>
     <row r="31" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="25" t="str">
+      <c r="B31" s="26" t="str">
         <f aca="false">IF(LEN(B28)&lt;40,"",IF(AND(ISNUMBER(SEARCH("skap",B28)),ISNUMBER(SEARCH("strøm",B28))),"Bra: du bruker begge eksemplene. Sier Nordlys nei til jobben, kjøpes ikke skapet (direkte og variabel), mens strømmen på verkstedet er felles (indirekte) og likevel varierer.",IF(OR(ISNUMBER(SEARCH("skap",B28)),ISNUMBER(SEARCH("strøm",B28))),"Du har ett av eksemplene. Ta med det andre også.","Tips: sier Nordlys nei til jobben, kjøpes ikke skapet; derfor er direkte alltid variabel. Husleia er indirekte og fast; strømmen på verkstedet er indirekte og variabel.")))</f>
         <v/>
       </c>
-      <c r="C31" s="25"/>
-      <c r="D31" s="25"/>
-      <c r="E31" s="25"/>
-      <c r="F31" s="25"/>
-      <c r="G31" s="25"/>
+      <c r="C31" s="26"/>
+      <c r="D31" s="26"/>
+      <c r="E31" s="26"/>
+      <c r="F31" s="26"/>
+      <c r="G31" s="26"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="17" t="s">
@@ -3219,35 +3433,35 @@
   </conditionalFormatting>
   <dataValidations count="9">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C13" type="list">
-      <formula1>"Direkte,Indirekte"</formula1>
+      <formula1>$Z$1:$Z$2</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C14" type="list">
-      <formula1>"Direkte,Indirekte"</formula1>
+      <formula1>$Z$3:$Z$4</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C15" type="list">
-      <formula1>"Direkte,Indirekte"</formula1>
+      <formula1>$Z$5:$Z$6</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C16" type="list">
-      <formula1>"Direkte,Indirekte"</formula1>
+      <formula1>$Z$7:$Z$8</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C17" type="list">
-      <formula1>"Direkte,Indirekte"</formula1>
+      <formula1>$Z$9:$Z$10</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C18" type="list">
-      <formula1>"Direkte,Indirekte"</formula1>
+      <formula1>$Z$11:$Z$12</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C19" type="list">
-      <formula1>"Direkte,Indirekte"</formula1>
+      <formula1>$Z$13:$Z$14</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C20" type="list">
-      <formula1>"Direkte,Indirekte"</formula1>
+      <formula1>$Z$15:$Z$16</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C32" type="list">
@@ -3270,7 +3484,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:G40"/>
+  <dimension ref="B1:Z40"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -3278,17 +3492,26 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="56"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="26" min="26" style="0" width="13"/>
   </cols>
   <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z1" s="0" t="s">
+        <v>97</v>
+      </c>
+    </row>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="5" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
+      <c r="Z2" s="20" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="6" t="s">
@@ -3299,6 +3522,9 @@
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
+      <c r="Z3" s="20" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="7" t="s">
@@ -3309,16 +3535,22 @@
       <c r="E4" s="7"/>
       <c r="F4" s="7"/>
       <c r="G4" s="7"/>
+      <c r="Z4" s="20" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="8" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
       <c r="E5" s="8"/>
       <c r="F5" s="8"/>
       <c r="G5" s="8"/>
+      <c r="Z5" s="20" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="7" t="s">
@@ -3329,51 +3561,71 @@
       <c r="E6" s="7"/>
       <c r="F6" s="7"/>
       <c r="G6" s="7"/>
+      <c r="Z6" s="20" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="8" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
       <c r="E7" s="8"/>
       <c r="F7" s="8"/>
       <c r="G7" s="8"/>
+      <c r="Z7" s="20" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z8" s="0" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="7" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
       <c r="E9" s="7"/>
       <c r="F9" s="7"/>
       <c r="G9" s="7"/>
+      <c r="Z9" s="20" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="8" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
       <c r="E10" s="8"/>
       <c r="F10" s="8"/>
       <c r="G10" s="8"/>
+      <c r="Z10" s="20" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="9" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>114</v>
+        <v>122</v>
+      </c>
+      <c r="Z11" s="20" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="11" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="C12" s="12" t="n">
         <v>6</v>
@@ -3381,10 +3633,13 @@
       <c r="D12" s="12" t="n">
         <v>6500</v>
       </c>
+      <c r="Z12" s="20" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="11" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="C13" s="12" t="n">
         <v>12</v>
@@ -3395,7 +3650,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="11" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="C14" s="12" t="n">
         <v>1</v>
@@ -3406,7 +3661,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="11" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="C15" s="12" t="n">
         <v>12</v>
@@ -3417,7 +3672,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="11" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="C16" s="12" t="n">
         <v>6</v>
@@ -3438,7 +3693,7 @@
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="8" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="C19" s="8"/>
       <c r="D19" s="8"/>
@@ -3447,107 +3702,107 @@
       <c r="G19" s="8"/>
     </row>
     <row r="21" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="21" t="s">
-        <v>121</v>
+      <c r="B21" s="22" t="s">
+        <v>129</v>
       </c>
       <c r="C21" s="14"/>
-      <c r="D21" s="23" t="s">
-        <v>73</v>
-      </c>
-      <c r="G21" s="22" t="str">
+      <c r="D21" s="24" t="s">
+        <v>79</v>
+      </c>
+      <c r="G21" s="23" t="str">
         <f aca="false">IF(C21="","Skriv svaret i den gule cellen.",IF(C21=(6*6500+12*640+800),"Riktig.",IF(ABS(C21-(6*6500+12*640))&lt;=0,"Du har glemt kjøringen, 800 kr.",IF(ABS(C21-(6*6500+800))&lt;=0,"Du har glemt montørtimene, 12 × 640 = 7 680.",IF(ABS(C21-(6500+2*640+800))&lt;=0,"Du har regnet ett ladepunkt. Det er seks.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene.")))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="21" t="s">
-        <v>122</v>
+      <c r="B22" s="22" t="s">
+        <v>130</v>
       </c>
       <c r="C22" s="14"/>
-      <c r="D22" s="23" t="s">
-        <v>73</v>
-      </c>
-      <c r="G22" s="22" t="str">
+      <c r="D22" s="24" t="s">
+        <v>79</v>
+      </c>
+      <c r="G22" s="23" t="str">
         <f aca="false">IF(C22="","Skriv svaret i den gule cellen.",IF(C22=(6*6500+12*640+800+12*267),"Riktig.",IF(ABS(C22-(6*6500+12*640+800))&lt;=0,"Det er bare de direkte. Legg til 12 × 267 = 3 204.",IF(ABS(C22-(6*6500+12*640+800+267))&lt;=0,"Du har lagt til 267 én gang. Det er 267 per montørtime, og jobben har 12 timer.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="21" t="s">
-        <v>123</v>
+      <c r="B23" s="22" t="s">
+        <v>131</v>
       </c>
       <c r="C23" s="14"/>
-      <c r="D23" s="23" t="s">
-        <v>73</v>
-      </c>
-      <c r="G23" s="22" t="str">
+      <c r="D23" s="24" t="s">
+        <v>79</v>
+      </c>
+      <c r="G23" s="23" t="str">
         <f aca="false">IF(C23="","Skriv svaret i den gule cellen.",IF(C23=(6*8830-(6*6500+12*640+800+12*267)),"Riktig.",IF(ABS(C23-(6*8830-(6*6500+12*640+800)))&lt;=0,"Du har trukket fra bare de direkte kostnadene. Trekk fra selvkosten, med den indirekte andelen.",IF(ABS(C23-(8830-(6500+2*640+800/6+2*267)))&lt;=0,"Du har regnet per ladepunkt. Oppgaven spør om hele jobben.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="21" t="s">
-        <v>124</v>
+      <c r="B25" s="22" t="s">
+        <v>132</v>
       </c>
       <c r="C25" s="18"/>
-      <c r="G25" s="22" t="str">
+      <c r="G25" s="23" t="str">
         <f aca="false">IF(C25="","Velg i nedtrekksmenyen.",IF(C25="Direkte","Riktig. Kjøpt til denne jobben.","Ikke riktig. Kjøpt til denne jobben."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="21" t="s">
-        <v>125</v>
+      <c r="B26" s="22" t="s">
+        <v>133</v>
       </c>
       <c r="C26" s="18"/>
-      <c r="G26" s="22" t="str">
+      <c r="G26" s="23" t="str">
         <f aca="false">IF(C26="","Velg i nedtrekksmenyen.",IF(C26="Direkte","Riktig. Brukt på denne jobben.","Ikke riktig. Brukt på denne jobben."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="21" t="s">
-        <v>126</v>
+      <c r="B27" s="22" t="s">
+        <v>134</v>
       </c>
       <c r="C27" s="18"/>
-      <c r="G27" s="22" t="str">
+      <c r="G27" s="23" t="str">
         <f aca="false">IF(C27="","Velg i nedtrekksmenyen.",IF(C27="Direkte","Riktig. Gjelder denne jobben.","Ikke riktig. Gjelder denne jobben."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="21" t="s">
-        <v>127</v>
+      <c r="B28" s="22" t="s">
+        <v>135</v>
       </c>
       <c r="C28" s="18"/>
-      <c r="G28" s="22" t="str">
+      <c r="G28" s="23" t="str">
         <f aca="false">IF(C28="","Velg i nedtrekksmenyen.",IF(C28="Indirekte","Riktig. Fordeles på alle jobbene.","Ikke riktig. Fordeles på alle jobbene."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="21" t="s">
-        <v>128</v>
+      <c r="B29" s="22" t="s">
+        <v>136</v>
       </c>
       <c r="C29" s="18"/>
-      <c r="G29" s="22" t="str">
+      <c r="G29" s="23" t="str">
         <f aca="false">IF(C29="","Velg i nedtrekksmenyen.",IF(C29="Indirekte","Riktig. Felles for alle jobbene.","Ikke riktig. Felles for alle jobbene."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="21" t="s">
-        <v>129</v>
+      <c r="B30" s="22" t="s">
+        <v>137</v>
       </c>
       <c r="C30" s="18"/>
-      <c r="G30" s="22" t="str">
+      <c r="G30" s="23" t="str">
         <f aca="false">IF(C30="","Velg i nedtrekksmenyen.",IF(C30="Indirekte","Riktig. Felles for alle jobbene.","Ikke riktig. Felles for alle jobbene."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="8" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="C32" s="8"/>
       <c r="D32" s="8"/>
@@ -3556,39 +3811,39 @@
       <c r="G32" s="8"/>
     </row>
     <row r="33" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B33" s="24"/>
-      <c r="C33" s="24"/>
-      <c r="D33" s="24"/>
-      <c r="E33" s="24"/>
-      <c r="F33" s="24"/>
-      <c r="G33" s="24"/>
+      <c r="B33" s="25"/>
+      <c r="C33" s="25"/>
+      <c r="D33" s="25"/>
+      <c r="E33" s="25"/>
+      <c r="F33" s="25"/>
+      <c r="G33" s="25"/>
     </row>
     <row r="34" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="24"/>
-      <c r="C34" s="24"/>
-      <c r="D34" s="24"/>
-      <c r="E34" s="24"/>
-      <c r="F34" s="24"/>
-      <c r="G34" s="24"/>
+      <c r="B34" s="25"/>
+      <c r="C34" s="25"/>
+      <c r="D34" s="25"/>
+      <c r="E34" s="25"/>
+      <c r="F34" s="25"/>
+      <c r="G34" s="25"/>
     </row>
     <row r="35" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B35" s="24"/>
-      <c r="C35" s="24"/>
-      <c r="D35" s="24"/>
-      <c r="E35" s="24"/>
-      <c r="F35" s="24"/>
-      <c r="G35" s="24"/>
+      <c r="B35" s="25"/>
+      <c r="C35" s="25"/>
+      <c r="D35" s="25"/>
+      <c r="E35" s="25"/>
+      <c r="F35" s="25"/>
+      <c r="G35" s="25"/>
     </row>
     <row r="36" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B36" s="25" t="str">
+      <c r="B36" s="26" t="str">
         <f aca="false">IF(LEN(B33)&lt;40,"",IF(AND(ISNUMBER(SEARCH("timer",B33)),ISNUMBER(SEARCH("267",B33))),"Bra: du peker på timene og på satsen for indirekte. Det er de to usikre leddene: tar jobben tre timer per punkt i stedet for to, er fortjenesten borte.",IF(OR(ISNUMBER(SEARCH("timer",B33)),ISNUMBER(SEARCH("267",B33))),"Du har med ett usikkert ledd. Se også på det andre: antall timer per ladepunkt, og om 267 kr per time dekker de indirekte kostnadene.","Tips: fortjenesten er 2 296 av 52 980, altså 4,3 %. Tar hvert ladepunkt tre timer i stedet for to, øker kostnadene med 6 × 907 = 5 442, og jobben går med tap. Kari bør sjekke timene og satsen for indirekte.")))</f>
         <v/>
       </c>
-      <c r="C36" s="25"/>
-      <c r="D36" s="25"/>
-      <c r="E36" s="25"/>
-      <c r="F36" s="25"/>
-      <c r="G36" s="25"/>
+      <c r="C36" s="26"/>
+      <c r="D36" s="26"/>
+      <c r="E36" s="26"/>
+      <c r="F36" s="26"/>
+      <c r="G36" s="26"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="17" t="s">
@@ -3709,27 +3964,27 @@
   </conditionalFormatting>
   <dataValidations count="7">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C25" type="list">
-      <formula1>"Direkte,Indirekte"</formula1>
+      <formula1>$Z$1:$Z$2</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C26" type="list">
-      <formula1>"Direkte,Indirekte"</formula1>
+      <formula1>$Z$3:$Z$4</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C27" type="list">
-      <formula1>"Direkte,Indirekte"</formula1>
+      <formula1>$Z$5:$Z$6</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C28" type="list">
-      <formula1>"Direkte,Indirekte"</formula1>
+      <formula1>$Z$7:$Z$8</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C29" type="list">
-      <formula1>"Direkte,Indirekte"</formula1>
+      <formula1>$Z$9:$Z$10</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C30" type="list">
-      <formula1>"Direkte,Indirekte"</formula1>
+      <formula1>$Z$11:$Z$12</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C37" type="list">
@@ -3762,287 +4017,287 @@
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="26" t="s">
-        <v>131</v>
+      <c r="B2" s="27" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="6" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="27" t="s">
-        <v>133</v>
-      </c>
-      <c r="C5" s="27" t="s">
-        <v>134</v>
-      </c>
-      <c r="D5" s="27" t="s">
-        <v>135</v>
+      <c r="B5" s="28" t="s">
+        <v>141</v>
+      </c>
+      <c r="C5" s="28" t="s">
+        <v>142</v>
+      </c>
+      <c r="D5" s="28" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="28" t="s">
-        <v>136</v>
+      <c r="B6" s="29" t="s">
+        <v>144</v>
       </c>
       <c r="C6" s="13" t="n">
         <v>720000</v>
       </c>
-      <c r="D6" s="28" t="s">
-        <v>137</v>
+      <c r="D6" s="29" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="28" t="s">
-        <v>138</v>
+      <c r="B7" s="29" t="s">
+        <v>146</v>
       </c>
       <c r="C7" s="13" t="n">
         <v>890000</v>
       </c>
-      <c r="D7" s="28" t="s">
-        <v>139</v>
+      <c r="D7" s="29" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="28" t="s">
-        <v>140</v>
+      <c r="B8" s="29" t="s">
+        <v>148</v>
       </c>
       <c r="C8" s="13"/>
-      <c r="D8" s="28" t="s">
-        <v>141</v>
+      <c r="D8" s="29" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="28" t="s">
-        <v>142</v>
+      <c r="B9" s="29" t="s">
+        <v>150</v>
       </c>
       <c r="C9" s="13" t="n">
         <v>267</v>
       </c>
-      <c r="D9" s="28" t="s">
-        <v>143</v>
+      <c r="D9" s="29" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="28" t="s">
-        <v>144</v>
+      <c r="B10" s="29" t="s">
+        <v>152</v>
       </c>
       <c r="C10" s="13" t="n">
         <v>384</v>
       </c>
-      <c r="D10" s="28" t="s">
-        <v>145</v>
+      <c r="D10" s="29" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="28" t="s">
-        <v>146</v>
+      <c r="B11" s="29" t="s">
+        <v>154</v>
       </c>
       <c r="C11" s="13" t="n">
         <v>800000</v>
       </c>
-      <c r="D11" s="28" t="s">
-        <v>147</v>
+      <c r="D11" s="29" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="28" t="s">
-        <v>148</v>
+      <c r="B12" s="29" t="s">
+        <v>156</v>
       </c>
       <c r="C12" s="13" t="n">
         <v>640000</v>
       </c>
-      <c r="D12" s="28" t="s">
-        <v>149</v>
+      <c r="D12" s="29" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="28" t="s">
-        <v>150</v>
+      <c r="B13" s="29" t="s">
+        <v>158</v>
       </c>
       <c r="C13" s="13" t="n">
         <v>90000</v>
       </c>
-      <c r="D13" s="28" t="s">
-        <v>151</v>
+      <c r="D13" s="29" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="28" t="s">
-        <v>152</v>
+      <c r="B14" s="29" t="s">
+        <v>160</v>
       </c>
       <c r="C14" s="13"/>
-      <c r="D14" s="28" t="s">
-        <v>153</v>
+      <c r="D14" s="29" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="28" t="s">
-        <v>154</v>
+      <c r="B15" s="29" t="s">
+        <v>162</v>
       </c>
       <c r="C15" s="13"/>
-      <c r="D15" s="28" t="s">
-        <v>155</v>
+      <c r="D15" s="29" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="28" t="s">
-        <v>156</v>
+      <c r="B16" s="29" t="s">
+        <v>164</v>
       </c>
       <c r="C16" s="13" t="n">
         <v>822080</v>
       </c>
-      <c r="D16" s="28" t="s">
-        <v>157</v>
+      <c r="D16" s="29" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="28" t="s">
-        <v>158</v>
+      <c r="B17" s="29" t="s">
+        <v>166</v>
       </c>
       <c r="C17" s="13" t="n">
         <v>836640</v>
       </c>
-      <c r="D17" s="28" t="s">
-        <v>159</v>
+      <c r="D17" s="29" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="28" t="s">
-        <v>160</v>
+      <c r="B18" s="29" t="s">
+        <v>168</v>
       </c>
       <c r="C18" s="13" t="n">
         <v>784000</v>
       </c>
-      <c r="D18" s="28" t="s">
-        <v>161</v>
+      <c r="D18" s="29" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="28" t="s">
-        <v>162</v>
+      <c r="B19" s="29" t="s">
+        <v>170</v>
       </c>
       <c r="C19" s="13" t="n">
         <v>311</v>
       </c>
-      <c r="D19" s="28" t="s">
-        <v>163</v>
+      <c r="D19" s="29" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="28" t="s">
-        <v>164</v>
+      <c r="B20" s="29" t="s">
+        <v>172</v>
       </c>
       <c r="C20" s="13" t="n">
         <v>457</v>
       </c>
-      <c r="D20" s="28" t="s">
-        <v>165</v>
+      <c r="D20" s="29" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="28" t="s">
-        <v>166</v>
+      <c r="B21" s="29" t="s">
+        <v>174</v>
       </c>
       <c r="C21" s="13" t="n">
         <v>587</v>
       </c>
-      <c r="D21" s="28" t="s">
-        <v>167</v>
+      <c r="D21" s="29" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="28" t="s">
-        <v>168</v>
+      <c r="B22" s="29" t="s">
+        <v>176</v>
       </c>
       <c r="C22" s="13"/>
-      <c r="D22" s="28" t="s">
-        <v>169</v>
+      <c r="D22" s="29" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="28" t="s">
-        <v>170</v>
+      <c r="B23" s="29" t="s">
+        <v>178</v>
       </c>
       <c r="C23" s="13"/>
-      <c r="D23" s="28" t="s">
-        <v>171</v>
+      <c r="D23" s="29" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="28" t="s">
-        <v>172</v>
+      <c r="B24" s="29" t="s">
+        <v>180</v>
       </c>
       <c r="C24" s="13" t="n">
         <v>19560</v>
       </c>
-      <c r="D24" s="28" t="s">
-        <v>173</v>
+      <c r="D24" s="29" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="28" t="s">
-        <v>174</v>
+      <c r="B25" s="29" t="s">
+        <v>182</v>
       </c>
       <c r="C25" s="13" t="n">
         <v>23760</v>
       </c>
-      <c r="D25" s="28" t="s">
-        <v>175</v>
+      <c r="D25" s="29" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="28" t="s">
-        <v>176</v>
+      <c r="B26" s="29" t="s">
+        <v>184</v>
       </c>
       <c r="C26" s="13" t="n">
         <v>47480</v>
       </c>
-      <c r="D26" s="28" t="s">
-        <v>177</v>
+      <c r="D26" s="29" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="28" t="s">
-        <v>178</v>
+      <c r="B27" s="29" t="s">
+        <v>186</v>
       </c>
       <c r="C27" s="13" t="n">
         <v>50684</v>
       </c>
-      <c r="D27" s="28" t="s">
-        <v>179</v>
+      <c r="D27" s="29" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="28" t="s">
-        <v>180</v>
+      <c r="B28" s="29" t="s">
+        <v>188</v>
       </c>
       <c r="C28" s="13" t="n">
         <v>2296</v>
       </c>
-      <c r="D28" s="28" t="s">
-        <v>181</v>
+      <c r="D28" s="29" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="28" t="s">
-        <v>182</v>
+      <c r="B29" s="29" t="s">
+        <v>190</v>
       </c>
       <c r="C29" s="13"/>
-      <c r="D29" s="28" t="s">
-        <v>183</v>
+      <c r="D29" s="29" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="28" t="s">
-        <v>184</v>
+      <c r="B30" s="29" t="s">
+        <v>192</v>
       </c>
       <c r="C30" s="13"/>
-      <c r="D30" s="28" t="s">
-        <v>185</v>
+      <c r="D30" s="29" t="s">
+        <v>193</v>
       </c>
     </row>
   </sheetData>

--- a/pensum/ok02/OK02_Viktige_begreper_Oppgaver_v6.xlsx
+++ b/pensum/ok02/OK02_Viktige_begreper_Oppgaver_v6.xlsx
@@ -68,7 +68,7 @@
     <t xml:space="preserve">2B  Jobb 2614 hos Hansen: direkte, indirekte og selvkost</t>
   </si>
   <si>
-    <t xml:space="preserve">2C  Seks ladepunkter til borettslaget: lønner jobben seg?</t>
+    <t xml:space="preserve">2C  Felles ladeanlegg med seks plasser i borettslaget: lønner jobben seg?</t>
   </si>
   <si>
     <t xml:space="preserve">Fasit  Alle svar med regnestykket skrevet ut</t>
@@ -86,7 +86,7 @@
     <t xml:space="preserve">Situasjonen</t>
   </si>
   <si>
-    <t xml:space="preserve">Ida er kalkulatør og innkjøper hos Nordlys Elektro. Hun kjøper kabel, vern og tavlemateriell hos Polarlys Elektro Grossist, som gir 30 dagers kreditt: det som kjøpes i én måned, betales måneden etter. Lageret var 1 250 000 kr 1. mars, og februarkjøpet var 760 000 kr. Mars er regnet ferdig. Du regner april.</t>
+    <t xml:space="preserve">Ronny Fjeld er formann på prosjektene hos Nordlys Elektro og bestiller kabel, vern og tavlemateriell til jobbene hos Polarlys Elektro Grossist, som gir 30 dagers kreditt: det som kjøpes i én måned, betales måneden etter. Lageret var 1 250 000 kr 1. mars, og februarkjøpet var 760 000 kr. Mars er regnet ferdig. Du regner april.</t>
   </si>
   <si>
     <t xml:space="preserve">Begrepene du trenger</t>
@@ -384,16 +384,16 @@
     <t xml:space="preserve">Hvorfor er direkte kostnader alltid variable, mens indirekte kan være både faste og variable? Bruk skapet og strømmen som eksempler.</t>
   </si>
   <si>
-    <t xml:space="preserve">Oppgave 2C: Seks ladepunkter til borettslaget: lønner jobben seg?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Borettslaget vil ha seks ladepunkter på parkeringsplassen. Ida har regnet et tilbud på 8 830 kr per ladepunkt. Kari spør om jobben lønner seg, og hva som kan gå galt.</t>
+    <t xml:space="preserve">Oppgave 2C: Felles ladeanlegg med seks plasser i borettslaget: lønner jobben seg?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Borettslaget vil ha et felles ladeanlegg med seks plasser på parkeringsplassen. Det er et lite prosjekt: ladebokser, ny kurs fra tavla, lastbalansering og kabelføring. Ida har regnet et tilbud på 124 590 kr uten merverdiavgift, om lag 20 800 kr per plass. Kari spør om jobben lønner seg, og hva som kan gå galt.</t>
   </si>
   <si>
     <t xml:space="preserve">Selvkost = direkte kostnader + andel indirekte. Fortjeneste = pris − selvkost. Satsen for indirekte, 267 kr per montørtime, er Nordlys' faste kostnader delt på fakturerte timer (fra oppgave 1B).</t>
   </si>
   <si>
-    <t xml:space="preserve">Hvert ladepunkt krever ladeboks og materiell for 6 500 kr og to montørtimer. Ida regner direkte lønnskostnad med 640 kr per time, og kjøringen til borettslaget koster 800 kr. De indirekte kostnadene fordeler hun med 267 kr per montørtime (3 840 000 / 14 400, avrundet). Prisen er 8 830 kr per ladepunkt uten merverdiavgift.</t>
+    <t xml:space="preserve">Et felles ladeanlegg i et borettslag er et prosjekt, ikke seks eneboligladere: det trengs seks ladebokser (6 × 6 500 = 39 000 kr) og felles infrastruktur med tavle, lastbalansering og kabel (27 000 kr), til sammen 66 000 kr i materiell. Ida anslår 51 montørtimer. Hun regner direkte lønnskostnad med 640 kr per time, og kjøringen er 800 kr per dag i to dager. De indirekte kostnadene fordeler hun med 267 kr per montørtime (3 840 000 / 14 400, avrundet). Tilbudet er regnet slik Nordlys alltid priser: 51 × 890 + 66 000 × 1,20 = 124 590 kr uten merverdiavgift, om lag 20 800 kr per plass.</t>
   </si>
   <si>
     <t xml:space="preserve">Post</t>
@@ -405,37 +405,37 @@
     <t xml:space="preserve">Kr per enhet</t>
   </si>
   <si>
-    <t xml:space="preserve">Ladeboks og materiell</t>
+    <t xml:space="preserve">Materiell: 6 ladebokser (39 000) og felles infrastruktur (27 000)</t>
   </si>
   <si>
     <t xml:space="preserve">Montørtimer (timesats)</t>
   </si>
   <si>
-    <t xml:space="preserve">Kjøring til borettslaget</t>
+    <t xml:space="preserve">Kjøring, to dager</t>
   </si>
   <si>
     <t xml:space="preserve">Indirekte, per montørtime</t>
   </si>
   <si>
-    <t xml:space="preserve">Pris til kunden, uten merverdiavgift</t>
+    <t xml:space="preserve">Pris til kunden uten merverdiavgift (51 × 890 + 66 000 × 1,20)</t>
   </si>
   <si>
     <t xml:space="preserve">1. Regn de direkte kostnadene: materiell, montørtimer og kjøring.
-2. Legg til andelen indirekte (12 timer × 267) og få selvkosten.
-3. Regn prisen for seks ladepunkt, og fortjenesten (pris minus selvkost).
+2. Legg til andelen indirekte (51 timer × 267) og få selvkosten.
+3. Regn fortjenesten: tilbudsprisen 124 590 minus selvkost.
 4. Svar på d og e.</t>
   </si>
   <si>
     <t xml:space="preserve">a) Sum direkte kostnader</t>
   </si>
   <si>
-    <t xml:space="preserve">b) Selvkost (direkte + 12 timer × 267)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c) Fortjeneste (6 × 8 830 minus selvkost)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">d) Er dette direkte for ladepunktjobben? Ladeboksene</t>
+    <t xml:space="preserve">b) Selvkost (direkte + 51 timer × 267)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c) Fortjeneste (124 590 minus selvkost)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d) Er dette direkte for ladepunktjobben? Ladeboksene og infrastrukturen</t>
   </si>
   <si>
     <t xml:space="preserve">d) Er dette direkte for ladepunktjobben? Montørtimene på borettslaget</t>
@@ -453,7 +453,7 @@
     <t xml:space="preserve">d) Er dette direkte for ladepunktjobben? Forsikringen på bilene</t>
   </si>
   <si>
-    <t xml:space="preserve">e) Fortjenesten i c er liten i prosent av prisen. Hva er usikkert i kalkylen, og hva bør Kari se etter før hun sier ja til jobben?</t>
+    <t xml:space="preserve">e) Fortjenesten i c er 8,6 % av prisen. Hva er usikkert i kalkylen, og hva bør Kari se etter før hun sier ja til jobben?</t>
   </si>
   <si>
     <t xml:space="preserve">Fasit, kapittel 2</t>
@@ -486,7 +486,7 @@
     <t xml:space="preserve">1B Sorteringen</t>
   </si>
   <si>
-    <t xml:space="preserve">Fast: husleie, forsikring, avskrivning, kontorlønn, strøm på verkstedet, kurs. Variabel: materiell, innleie, drivstoff, montørtimene. Kommer an på: lærlingens lønn, leasing.</t>
+    <t xml:space="preserve">Fast: husleie, forsikring, avskrivning, kontorlønn, strøm på verkstedet, kurs. Variabel: materiell, innleie, drivstoff. Kommer an på: montørtimene (variable i kalkylen, men fast lønn på kort sikt), lærlingens lønn, leasing.</t>
   </si>
   <si>
     <t xml:space="preserve">1B Faste per time, 14 400 timer</t>
@@ -594,31 +594,31 @@
     <t xml:space="preserve">2C a) Direkte</t>
   </si>
   <si>
-    <t xml:space="preserve">39 000 + 7 680 + 800 = 47 480 kr</t>
+    <t xml:space="preserve">66 000 + 32 640 + 1 600 = 100 240 kr</t>
   </si>
   <si>
     <t xml:space="preserve">2C b) Selvkost</t>
   </si>
   <si>
-    <t xml:space="preserve">47 480 + 3 204 = 50 684 kr</t>
+    <t xml:space="preserve">100 240 + 13 617 = 113 857 kr</t>
   </si>
   <si>
     <t xml:space="preserve">2C c) Fortjeneste</t>
   </si>
   <si>
-    <t xml:space="preserve">52 980 − 50 684 = 2 296 kr (4,3 % av prisen)</t>
+    <t xml:space="preserve">124 590 − 113 857 = 10 733 kr (8,6 % av prisen)</t>
   </si>
   <si>
     <t xml:space="preserve">2C d) Sorteringen</t>
   </si>
   <si>
-    <t xml:space="preserve">Direkte: ladebokser, montørtimer, kjøring. Indirekte: Idas tid, husleie, forsikring</t>
+    <t xml:space="preserve">Direkte: ladebokser og infrastruktur, montørtimer, kjøring. Indirekte: Idas tid, husleie, forsikring</t>
   </si>
   <si>
     <t xml:space="preserve">2C e) Usikkert</t>
   </si>
   <si>
-    <t xml:space="preserve">Timene per ladepunkt og satsen 267 kr. Tre timer i stedet for to gir tap. Kari bør sjekke timene mot erfaringen fra liknende jobber</t>
+    <t xml:space="preserve">Timeanslaget og satsen 267 kr. Ti timer for mye spiser 9 070 av 10 733. Kari bør sjekke timeanslaget mot liknende anlegg og befare tavla før hun sier ja</t>
   </si>
 </sst>
 </file>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="C20" s="18"/>
       <c r="G20" s="23" t="str">
-        <f aca="false">IF(C20="","Velg i nedtrekksmenyen.",IF(C20="Variabel","Riktig. Boka regner montørlønn som variabel: timene følger jobbene (vei 1 i kapittel 2).","Ikke riktig. Boka regner montørlønn som variabel: timene følger jobbene (vei 1 i kapittel 2)."))</f>
+        <f aca="false">IF(C20="","Velg i nedtrekksmenyen.",IF(C20="Kommer an på","Riktig. I kalkylen og på lang sikt er timene en direkte, variabel kostnad, slik boka regner. Men de 12 montørene er fast ansatt: i juli, på kort sikt, løper lønna uansett om timene faktureres.","Ikke riktig. I kalkylen og på lang sikt er timene en direkte, variabel kostnad, slik boka regner. Men de 12 montørene er fast ansatt: i juli, på kort sikt, løper lønna uansett om timene faktureres."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
       <c r="Z20" s="20" t="s">
@@ -1995,7 +1995,7 @@
     </row>
     <row r="35" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="26" t="str">
-        <f aca="false">IF(LEN(B32)&lt;40,"",IF(AND(ISNUMBER(SEARCH("stille",B32)),ISNUMBER(SEARCH("pris",B32))),"Bra: du har med både at de faste per time stiger når det blir stille, og hva det betyr for prisen.",IF(OR(ISNUMBER(SEARCH("stille",B32)),ISNUMBER(SEARCH("pris",B32))),"Du er på sporet. Si også hva det bør bety for timeprisen i en stille periode.","Tips: de faste kostnadene står stille i kroner, men per time stiger de når timene blir færre. Derfor må timeprisen opp, ikke ned, når det er stille.")))</f>
+        <f aca="false">IF(LEN(B32)&lt;40,"",IF(AND(ISNUMBER(SEARCH("stille",B32)),ISNUMBER(SEARCH("pris",B32))),"Bra: du har med både at de faste per time stiger når det blir stille, og hva det betyr for prisen.",IF(OR(ISNUMBER(SEARCH("stille",B32)),ISNUMBER(SEARCH("pris",B32))),"Du er på sporet. Si også hva det bør bety for timeprisen i en stille periode.","Tips: de faste kostnadene står stille i kroner, men per time stiger de når timene blir færre. Det betyr ikke at timeprisen skal opp: prisen bygger på normalaktiviteten (kapittel 5), og en høyere pris i en stille periode skremmer bort de jobbene som er igjen. Svaret er flere fakturerte timer.")))</f>
         <v/>
       </c>
       <c r="C35" s="26"/>
@@ -3539,7 +3539,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="8" t="s">
         <v>117</v>
       </c>
@@ -3596,7 +3596,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="8" t="s">
         <v>119</v>
       </c>
@@ -3628,10 +3628,10 @@
         <v>123</v>
       </c>
       <c r="C12" s="12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D12" s="12" t="n">
-        <v>6500</v>
+        <v>66000</v>
       </c>
       <c r="Z12" s="20" t="s">
         <v>99</v>
@@ -3642,7 +3642,7 @@
         <v>124</v>
       </c>
       <c r="C13" s="12" t="n">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="D13" s="12" t="n">
         <v>640</v>
@@ -3653,7 +3653,7 @@
         <v>125</v>
       </c>
       <c r="C14" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14" s="12" t="n">
         <v>800</v>
@@ -3664,7 +3664,7 @@
         <v>126</v>
       </c>
       <c r="C15" s="12" t="n">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="D15" s="12" t="n">
         <v>267</v>
@@ -3675,10 +3675,10 @@
         <v>127</v>
       </c>
       <c r="C16" s="12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>8830</v>
+        <v>124590</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3710,7 +3710,7 @@
         <v>79</v>
       </c>
       <c r="G21" s="23" t="str">
-        <f aca="false">IF(C21="","Skriv svaret i den gule cellen.",IF(C21=(6*6500+12*640+800),"Riktig.",IF(ABS(C21-(6*6500+12*640))&lt;=0,"Du har glemt kjøringen, 800 kr.",IF(ABS(C21-(6*6500+800))&lt;=0,"Du har glemt montørtimene, 12 × 640 = 7 680.",IF(ABS(C21-(6500+2*640+800))&lt;=0,"Du har regnet ett ladepunkt. Det er seks.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene.")))))</f>
+        <f aca="false">IF(C21="","Skriv svaret i den gule cellen.",IF(C21=(66000+51*640+2*800),"Riktig.",IF(ABS(C21-(66000+51*640))&lt;=0,"Du har glemt kjøringen, 2 × 800 = 1 600 kr.",IF(ABS(C21-(66000+2*800))&lt;=0,"Du har glemt montørtimene, 51 × 640 = 32 640.",IF(ABS(C21-(39000+51*640+2*800))&lt;=0,"Du har glemt den felles infrastrukturen, 27 000 kr.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene.")))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
@@ -3723,7 +3723,7 @@
         <v>79</v>
       </c>
       <c r="G22" s="23" t="str">
-        <f aca="false">IF(C22="","Skriv svaret i den gule cellen.",IF(C22=(6*6500+12*640+800+12*267),"Riktig.",IF(ABS(C22-(6*6500+12*640+800))&lt;=0,"Det er bare de direkte. Legg til 12 × 267 = 3 204.",IF(ABS(C22-(6*6500+12*640+800+267))&lt;=0,"Du har lagt til 267 én gang. Det er 267 per montørtime, og jobben har 12 timer.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
+        <f aca="false">IF(C22="","Skriv svaret i den gule cellen.",IF(C22=(66000+51*640+2*800+51*267),"Riktig.",IF(ABS(C22-(66000+51*640+2*800))&lt;=0,"Det er bare de direkte. Legg til 51 × 267 = 13 617.",IF(ABS(C22-(66000+51*640+2*800+267))&lt;=0,"Du har lagt til 267 én gang. Det er 267 per montørtime, og jobben har 51 timer.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
@@ -3736,7 +3736,7 @@
         <v>79</v>
       </c>
       <c r="G23" s="23" t="str">
-        <f aca="false">IF(C23="","Skriv svaret i den gule cellen.",IF(C23=(6*8830-(6*6500+12*640+800+12*267)),"Riktig.",IF(ABS(C23-(6*8830-(6*6500+12*640+800)))&lt;=0,"Du har trukket fra bare de direkte kostnadene. Trekk fra selvkosten, med den indirekte andelen.",IF(ABS(C23-(8830-(6500+2*640+800/6+2*267)))&lt;=0,"Du har regnet per ladepunkt. Oppgaven spør om hele jobben.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
+        <f aca="false">IF(C23="","Skriv svaret i den gule cellen.",IF(C23=(124590-(66000+51*640+2*800+51*267)),"Riktig.",IF(ABS(C23-(124590-(66000+51*640+2*800)))&lt;=0,"Du har trukket fra bare de direkte kostnadene. Trekk fra selvkosten, med den indirekte andelen.",IF(ABS(C23-(124590-66000))&lt;=0,"Du har trukket fra bare materiellet. Timene, kjøringen og de indirekte må også med.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
@@ -3756,7 +3756,7 @@
       </c>
       <c r="C26" s="18"/>
       <c r="G26" s="23" t="str">
-        <f aca="false">IF(C26="","Velg i nedtrekksmenyen.",IF(C26="Direkte","Riktig. Brukt på denne jobben.","Ikke riktig. Brukt på denne jobben."))</f>
+        <f aca="false">IF(C26="","Velg i nedtrekksmenyen.",IF(C26="Direkte","Riktig. Brukt på denne jobben (i kalkylen er timene en direkte kostnad).","Ikke riktig. Brukt på denne jobben (i kalkylen er timene en direkte kostnad)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
@@ -3836,7 +3836,7 @@
     </row>
     <row r="36" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B36" s="26" t="str">
-        <f aca="false">IF(LEN(B33)&lt;40,"",IF(AND(ISNUMBER(SEARCH("timer",B33)),ISNUMBER(SEARCH("267",B33))),"Bra: du peker på timene og på satsen for indirekte. Det er de to usikre leddene: tar jobben tre timer per punkt i stedet for to, er fortjenesten borte.",IF(OR(ISNUMBER(SEARCH("timer",B33)),ISNUMBER(SEARCH("267",B33))),"Du har med ett usikkert ledd. Se også på det andre: antall timer per ladepunkt, og om 267 kr per time dekker de indirekte kostnadene.","Tips: fortjenesten er 2 296 av 52 980, altså 4,3 %. Tar hvert ladepunkt tre timer i stedet for to, øker kostnadene med 6 × 907 = 5 442, og jobben går med tap. Kari bør sjekke timene og satsen for indirekte.")))</f>
+        <f aca="false">IF(LEN(B33)&lt;40,"",IF(AND(ISNUMBER(SEARCH("timer",B33)),ISNUMBER(SEARCH("267",B33))),"Bra: du peker på timene og på satsen for indirekte. Det er de to usikre leddene: bruker jobben 61 timer i stedet for 51, er nesten hele fortjenesten borte.",IF(OR(ISNUMBER(SEARCH("timer",B33)),ISNUMBER(SEARCH("267",B33))),"Du har med ett usikkert ledd. Se også på det andre: timeanslaget for infrastrukturen, og om 267 kr per time dekker de indirekte kostnadene.","Tips: fortjenesten er 10 733 av 124 590, altså 8,6 %. Bruker jobben ti timer mer enn anslått, øker kostnadene med 10 × 907 = 9 070, og det er bare 1 663 kr igjen. Kari bør sjekke timeanslaget (befaring av tavla og kabelføringen) og satsen for indirekte.")))</f>
         <v/>
       </c>
       <c r="C36" s="26"/>
@@ -3853,7 +3853,7 @@
     </row>
     <row r="38" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="19" t="str">
-        <f aca="false">IF(C37="JA","Hint: a: 6 × 6 500 + 12 × 640 + 800 = 47 480. b: 47 480 + 12 × 267 = 50 684. c: 6 × 8 830 − 50 684 = 2 296.","")</f>
+        <f aca="false">IF(C37="JA","Hint: a: 66 000 + 51 × 640 + 2 × 800 = 100 240. b: 100 240 + 51 × 267 = 113 857. c: 124 590 − 113 857 = 10 733.","")</f>
         <v/>
       </c>
       <c r="C38" s="19"/>
@@ -4254,7 +4254,7 @@
         <v>184</v>
       </c>
       <c r="C26" s="13" t="n">
-        <v>47480</v>
+        <v>100240</v>
       </c>
       <c r="D26" s="29" t="s">
         <v>185</v>
@@ -4265,7 +4265,7 @@
         <v>186</v>
       </c>
       <c r="C27" s="13" t="n">
-        <v>50684</v>
+        <v>113857</v>
       </c>
       <c r="D27" s="29" t="s">
         <v>187</v>
@@ -4276,7 +4276,7 @@
         <v>188</v>
       </c>
       <c r="C28" s="13" t="n">
-        <v>2296</v>
+        <v>10733</v>
       </c>
       <c r="D28" s="29" t="s">
         <v>189</v>

--- a/pensum/ok02/OK02_Viktige_begreper_Oppgaver_v6.xlsx
+++ b/pensum/ok02/OK02_Viktige_begreper_Oppgaver_v6.xlsx
@@ -804,7 +804,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -923,6 +923,10 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment wrapText="true" horizontal="general" vertical="bottom" textRotation="0" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1210,7 +1214,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="3" t="s">
         <v>2</v>
       </c>
@@ -1235,42 +1239,42 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="11" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="15" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="16" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="17" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="18" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="2" t="s">
         <v>14</v>
       </c>
@@ -1376,7 +1380,7 @@
       <c r="F9" s="7"/>
       <c r="G9" s="7"/>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="8" t="s">
         <v>23</v>
       </c>
@@ -1710,7 +1714,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="21" t="s">
         <v>46</v>
       </c>
@@ -2329,7 +2333,7 @@
       <c r="F9" s="7"/>
       <c r="G9" s="7"/>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="8" t="s">
         <v>71</v>
       </c>
@@ -2426,7 +2430,7 @@
       <c r="F18" s="7"/>
       <c r="G18" s="7"/>
     </row>
-    <row r="19" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="60.75" customHeight="true" r="19" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="8" t="s">
         <v>77</v>
       </c>
@@ -2732,7 +2736,7 @@
       <c r="F12" s="7"/>
       <c r="G12" s="7"/>
     </row>
-    <row r="13" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="75.75" customHeight="true" r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="8" t="s">
         <v>89</v>
       </c>
@@ -3109,7 +3113,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="21" t="s">
         <v>103</v>
       </c>
@@ -3623,8 +3627,8 @@
         <v>97</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="11" t="s">
+    <row ht="31.5" customHeight="true" r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="30" r="B12" t="s">
         <v>123</v>
       </c>
       <c r="C12" s="12" t="n">
@@ -3670,8 +3674,8 @@
         <v>267</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="11" t="s">
+    <row ht="31.5" customHeight="true" r="16" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="30" r="B16" t="s">
         <v>127</v>
       </c>
       <c r="C16" s="12" t="n">
@@ -3691,7 +3695,7 @@
       <c r="F18" s="7"/>
       <c r="G18" s="7"/>
     </row>
-    <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="60.75" customHeight="true" r="19" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="8" t="s">
         <v>128</v>
       </c>
